--- a/storage/app/pdfs/ghg_download.xlsx
+++ b/storage/app/pdfs/ghg_download.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/rfavela_hcx_mx/Documents/F90/Operacion/Proyectos/Proyectos en curso/US Grains 013 (Analisis Global)/Entregables/America/1.  Informacion Latam/4. GHG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/ssantos_faro90_com/Documents/Escritorio/Archivos faltantes emisioens y GHG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{1967BE99-94C3-3542-978E-BB158703CD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE65ACA3-C233-E34A-BF3E-656E2808732E}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="13_ncr:1_{1967BE99-94C3-3542-978E-BB158703CD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A57E786-6E9E-45F8-92A0-D675CB9D732C}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="1280" windowWidth="27820" windowHeight="10580" tabRatio="853" firstSheet="3" activeTab="16" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="853" firstSheet="1" activeTab="1" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="7" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="36">
   <si>
     <t>Content</t>
   </si>
@@ -111,12 +111,6 @@
     <t>Uruguay</t>
   </si>
   <si>
-    <t>GHG Emissions</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
     <t>E0</t>
   </si>
   <si>
@@ -138,49 +132,47 @@
     <t>GREET 2024</t>
   </si>
   <si>
-    <t>Millon Ton/yr</t>
+    <t>RED II/III</t>
   </si>
   <si>
-    <t>RED II/III</t>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Life Cycle GHG Emissions</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>gCO2/MJ</t>
+  </si>
+  <si>
+    <t>GHG Emissions</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Millon Ton/yr</t>
   </si>
   <si>
     <t>%Reduction vs E0</t>
   </si>
   <si>
-    <t>%</t>
-  </si>
-  <si>
     <t>% 2035 Target</t>
-  </si>
-  <si>
-    <t>Life Cycle GHG Emissions</t>
-  </si>
-  <si>
-    <t>Emisiones GEI</t>
-  </si>
-  <si>
-    <t>Unidad</t>
-  </si>
-  <si>
-    <t>Millones Ton/año</t>
-  </si>
-  <si>
-    <t>%Reducción vs E0</t>
-  </si>
-  <si>
-    <t>% Meta@2035</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,13 +236,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -272,9 +257,30 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -301,8 +307,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD18316"/>
+        <bgColor rgb="FF4F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF002F60"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
@@ -311,8 +329,14 @@
         <bgColor theme="4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002F60"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -336,26 +360,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -368,17 +372,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -463,6 +456,46 @@
       </left>
       <right/>
       <top style="thin">
+        <color rgb="FF95B3D7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF95B3D7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF95B3D7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </top>
       <bottom/>
@@ -480,7 +513,7 @@
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -505,57 +538,69 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="4" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="6" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="6" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="6" borderId="5" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="11" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="6" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="6" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="8" borderId="12" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -957,120 +1002,120 @@
     <tabColor rgb="FF002F60"/>
   </sheetPr>
   <dimension ref="A1:A24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="80.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="80.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="5"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:1" ht="18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="29" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A6" s="29"/>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="28"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>18</v>
       </c>
@@ -1107,30 +1152,30 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -1144,7 +1189,7 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -1158,30 +1203,30 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A6" s="13" t="s">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="E6" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="F6" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="G6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="H6" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -1189,30 +1234,30 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>27</v>
+    <row r="7" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" s="19">
-        <v>16.944838312140856</v>
+        <v>16.924707296169579</v>
       </c>
       <c r="D7" s="19">
-        <v>15.252268295378054</v>
+        <v>15.269864765211961</v>
       </c>
       <c r="E7" s="19">
-        <v>14.767769287661089</v>
+        <v>14.780046196716361</v>
       </c>
       <c r="F7" s="19">
-        <v>14.203186047325506</v>
+        <v>14.226919781855328</v>
       </c>
       <c r="G7" s="19">
-        <v>13.754712084661925</v>
+        <v>13.77805551290181</v>
       </c>
       <c r="H7" s="19">
-        <v>13.158231435545122</v>
+        <v>13.185568386441531</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -1220,30 +1265,30 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
-        <v>29</v>
+    <row r="8" spans="1:13" s="9" customFormat="1" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C8" s="19">
-        <v>24.026472813260902</v>
+        <v>24.42106523898601</v>
       </c>
       <c r="D8" s="19">
-        <v>22.121300241824894</v>
+        <v>22.541169459497215</v>
       </c>
       <c r="E8" s="19">
-        <v>21.538263658468814</v>
+        <v>21.947042635938274</v>
       </c>
       <c r="F8" s="19">
-        <v>20.880691089734984</v>
+        <v>21.295481136574487</v>
       </c>
       <c r="G8" s="19">
-        <v>20.345080966624121</v>
+        <v>20.754377731532806</v>
       </c>
       <c r="H8" s="19">
-        <v>19.667645006469673</v>
+        <v>20.076194288944613</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -1251,30 +1296,30 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A9" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="14" t="s">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="E9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="F9" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="G9" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="H9" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -1282,30 +1327,30 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:13" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:13" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>9.9887056198706137E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>0.12847977563290838</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.16179866778964636</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.18826536840975511</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.22346668683658413</v>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>9.7776729724131997E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>0.12671776604010165</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.15939936018419759</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.18592060283251832</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.2209278331551586</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -1313,30 +1358,30 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
-        <v>29</v>
+    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="21">
-        <v>0</v>
-      </c>
-      <c r="D11" s="21">
-        <v>7.929472570707459E-2</v>
-      </c>
-      <c r="E11" s="21">
-        <v>0.10356114999196943</v>
-      </c>
-      <c r="F11" s="21">
-        <v>0.13092981845382107</v>
-      </c>
-      <c r="G11" s="21">
-        <v>0.15322231753488658</v>
-      </c>
-      <c r="H11" s="22">
-        <v>0.18141771539538948</v>
+        <v>27</v>
+      </c>
+      <c r="C11" s="23">
+        <v>0</v>
+      </c>
+      <c r="D11" s="23">
+        <v>7.6978451230199085E-2</v>
+      </c>
+      <c r="E11" s="23">
+        <v>0.10130690773874121</v>
+      </c>
+      <c r="F11" s="23">
+        <v>0.12798721398204252</v>
+      </c>
+      <c r="G11" s="23">
+        <v>0.1501444540428839</v>
+      </c>
+      <c r="H11" s="24">
+        <v>0.17791488239854522</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
@@ -1344,82 +1389,160 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A12" s="13" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="C12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="E12" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="F12" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="G12" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="H12" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="14" t="s">
+    </row>
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="B13" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="23">
+        <v>0</v>
+      </c>
+      <c r="D13" s="23">
+        <v>7.6133425301262936E-2</v>
+      </c>
+      <c r="E13" s="23">
+        <v>9.866823734416566E-2</v>
+      </c>
+      <c r="F13" s="23">
+        <v>0.1241156184696731</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0.14476626869861253</v>
+      </c>
+      <c r="H13" s="24">
+        <v>0.17202449631874783</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="B14" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="21">
-        <v>0</v>
-      </c>
-      <c r="D13" s="21">
-        <v>7.786913287985131E-2</v>
-      </c>
-      <c r="E13" s="21">
-        <v>0.10015921083138314</v>
-      </c>
-      <c r="F13" s="21">
-        <v>0.12613367979161738</v>
-      </c>
-      <c r="G13" s="21">
-        <v>0.14676637341488971</v>
-      </c>
-      <c r="H13" s="22">
-        <v>0.17420832882372492</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+      <c r="C14" s="25">
+        <v>0</v>
+      </c>
+      <c r="D14" s="25">
+        <v>8.6487325666598502E-2</v>
+      </c>
+      <c r="E14" s="25">
+        <v>0.11382098992450591</v>
+      </c>
+      <c r="F14" s="25">
+        <v>0.14379701955451921</v>
+      </c>
+      <c r="G14" s="25">
+        <v>0.16869126471521176</v>
+      </c>
+      <c r="H14" s="26">
+        <v>0.1998920753669437</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="23">
-        <v>0</v>
-      </c>
-      <c r="D14" s="23">
-        <v>8.7650221057288716E-2</v>
-      </c>
-      <c r="E14" s="23">
-        <v>0.11447366276636606</v>
-      </c>
-      <c r="F14" s="23">
-        <v>0.14472624034115572</v>
-      </c>
-      <c r="G14" s="23">
-        <v>0.1693677591174855</v>
-      </c>
-      <c r="H14" s="24">
-        <v>0.2005341807581974</v>
+      <c r="B15" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>169.57735616688672</v>
+      </c>
+      <c r="D16" s="27">
+        <v>152.99663684562418</v>
+      </c>
+      <c r="E16" s="27">
+        <v>148.08889242243217</v>
+      </c>
+      <c r="F16" s="27">
+        <v>142.54683409215718</v>
+      </c>
+      <c r="G16" s="27">
+        <v>138.0494318815945</v>
+      </c>
+      <c r="H16" s="27">
+        <v>132.11299831675584</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="27">
+        <v>244.68722593173371</v>
+      </c>
+      <c r="D17" s="27">
+        <v>225.85158224369502</v>
+      </c>
+      <c r="E17" s="27">
+        <v>219.898719709419</v>
+      </c>
+      <c r="F17" s="27">
+        <v>213.37038958773653</v>
+      </c>
+      <c r="G17" s="27">
+        <v>207.94879598294574</v>
+      </c>
+      <c r="H17" s="27">
+        <v>201.15372690566301</v>
       </c>
     </row>
   </sheetData>
@@ -1435,30 +1558,30 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -1472,7 +1595,7 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -1486,30 +1609,30 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="13" t="s">
+    <row r="6" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="E6" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="F6" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="G6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="H6" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -1517,30 +1640,30 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>27</v>
+    <row r="7" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" s="19">
-        <v>10.062099937080543</v>
+        <v>8.9490894706979081</v>
       </c>
       <c r="D7" s="19">
-        <v>9.0780572455645938</v>
+        <v>8.065491074841141</v>
       </c>
       <c r="E7" s="19">
-        <v>8.8104442357314756</v>
+        <v>7.8158993510519901</v>
       </c>
       <c r="F7" s="19">
-        <v>8.4936457323826424</v>
+        <v>7.5243704040166648</v>
       </c>
       <c r="G7" s="19">
-        <v>8.2498264303088078</v>
+        <v>7.2956870251052788</v>
       </c>
       <c r="H7" s="19">
-        <v>7.9162789252090731</v>
+        <v>6.9876425909690223</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -1548,30 +1671,30 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
-        <v>29</v>
+    <row r="8" spans="1:13" s="9" customFormat="1" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C8" s="19">
-        <v>13.164015510238267</v>
+        <v>12.452914714792714</v>
       </c>
       <c r="D8" s="19">
-        <v>12.081889955980243</v>
+        <v>11.458525034523618</v>
       </c>
       <c r="E8" s="19">
-        <v>11.768519357878551</v>
+        <v>11.157246993327336</v>
       </c>
       <c r="F8" s="19">
-        <v>11.408310029975487</v>
+        <v>10.816682558590058</v>
       </c>
       <c r="G8" s="19">
-        <v>11.123555640560449</v>
+        <v>10.541760206046865</v>
       </c>
       <c r="H8" s="19">
-        <v>10.751687386033561</v>
+        <v>10.190429871295718</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -1579,30 +1702,30 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A9" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="14" t="s">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="E9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="F9" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="G9" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="H9" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -1610,134 +1733,212 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>9.7796950703061991E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>0.12439308982973861</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.15587742265586937</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.18010887569235923</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.21325777176628469</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>9.8736122680406976E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>0.126626303531363</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.15920268440115778</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.18475649964238053</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.21917837408501398</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="23">
+        <v>0</v>
+      </c>
+      <c r="D11" s="23">
+        <v>7.9851962616259542E-2</v>
+      </c>
+      <c r="E11" s="23">
+        <v>0.10404533807063379</v>
+      </c>
+      <c r="F11" s="23">
+        <v>0.13139350856221549</v>
+      </c>
+      <c r="G11" s="23">
+        <v>0.15347045671770354</v>
+      </c>
+      <c r="H11" s="24">
+        <v>0.18168315573617544</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="23">
+        <v>0</v>
+      </c>
+      <c r="D13" s="23">
+        <v>5.7604273789879049E-2</v>
+      </c>
+      <c r="E13" s="23">
+        <v>7.3875862851442653E-2</v>
+      </c>
+      <c r="F13" s="23">
+        <v>9.2881457883577878E-2</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0.10778997291911392</v>
+      </c>
+      <c r="H13" s="24">
+        <v>0.12787225917793793</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="25">
+        <v>0</v>
+      </c>
+      <c r="D14" s="25">
+        <v>6.4827070380214541E-2</v>
+      </c>
+      <c r="E14" s="25">
+        <v>8.4468236382016948E-2</v>
+      </c>
+      <c r="F14" s="25">
+        <v>0.10667059328272104</v>
+      </c>
+      <c r="G14" s="25">
+        <v>0.12459355754014245</v>
+      </c>
+      <c r="H14" s="26">
+        <v>0.14749777385446852</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="21">
-        <v>0</v>
-      </c>
-      <c r="D11" s="21">
-        <v>8.2203302891614233E-2</v>
-      </c>
-      <c r="E11" s="21">
-        <v>0.10600839472381154</v>
-      </c>
-      <c r="F11" s="21">
-        <v>0.1333715748737371</v>
-      </c>
-      <c r="G11" s="21">
-        <v>0.15500284606098022</v>
-      </c>
-      <c r="H11" s="22">
-        <v>0.18325169264108856</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A12" s="13" t="s">
+      <c r="B15" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="C15" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="E15" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="F15" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="G15" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="H15" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="14" t="s">
+    </row>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>191.83746272475219</v>
+      </c>
+      <c r="D16" s="27">
+        <v>172.89617547046308</v>
+      </c>
+      <c r="E16" s="27">
+        <v>167.54579394108117</v>
+      </c>
+      <c r="F16" s="27">
+        <v>161.29642369026459</v>
+      </c>
+      <c r="G16" s="27">
+        <v>156.39424461145131</v>
+      </c>
+      <c r="H16" s="27">
+        <v>149.79083955614652</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="21">
-        <v>0</v>
-      </c>
-      <c r="D13" s="21">
-        <v>6.4152520974249228E-2</v>
-      </c>
-      <c r="E13" s="21">
-        <v>8.1598968546410106E-2</v>
-      </c>
-      <c r="F13" s="21">
-        <v>0.1022519572895996</v>
-      </c>
-      <c r="G13" s="21">
-        <v>0.11814722588421928</v>
-      </c>
-      <c r="H13" s="22">
-        <v>0.13989212933333189</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="23">
-        <v>0</v>
-      </c>
-      <c r="D14" s="23">
-        <v>7.0546819680519721E-2</v>
-      </c>
-      <c r="E14" s="23">
-        <v>9.0976333603804596E-2</v>
-      </c>
-      <c r="F14" s="23">
-        <v>0.1144593965467572</v>
-      </c>
-      <c r="G14" s="23">
-        <v>0.1330233390433127</v>
-      </c>
-      <c r="H14" s="24">
-        <v>0.15726648032556972</v>
+      <c r="B17" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="27">
+        <v>266.94733248959915</v>
+      </c>
+      <c r="D17" s="27">
+        <v>245.63106407512947</v>
+      </c>
+      <c r="E17" s="27">
+        <v>239.17270703366498</v>
+      </c>
+      <c r="F17" s="27">
+        <v>231.87218587246639</v>
+      </c>
+      <c r="G17" s="27">
+        <v>225.97880345284764</v>
+      </c>
+      <c r="H17" s="27">
+        <v>218.44749870753469</v>
       </c>
     </row>
   </sheetData>
@@ -1753,30 +1954,30 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1791,30 +1992,30 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -1822,30 +2023,30 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>27</v>
+    <row r="6" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C6" s="19">
-        <v>3.2227426513307416</v>
+        <v>4.4762425147804468</v>
       </c>
       <c r="D6" s="19">
-        <v>2.8670484454995524</v>
+        <v>4.0327034376058197</v>
       </c>
       <c r="E6" s="19">
-        <v>2.737899941575769</v>
+        <v>3.9004585075791454</v>
       </c>
       <c r="F6" s="19">
-        <v>2.5997747088709549</v>
+        <v>3.7518970612089015</v>
       </c>
       <c r="G6" s="19">
-        <v>2.4752441279329647</v>
+        <v>3.6305968903221855</v>
       </c>
       <c r="H6" s="19">
-        <v>2.3254927662656448</v>
+        <v>3.4711218036603064</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -1853,30 +2054,30 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>29</v>
+    <row r="7" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" s="19">
-        <v>6.3416623262044522</v>
+        <v>6.3595985083336419</v>
       </c>
       <c r="D7" s="19">
-        <v>5.8848562278448711</v>
+        <v>5.8550031332533763</v>
       </c>
       <c r="E7" s="19">
-        <v>5.708993190011622</v>
+        <v>5.694549686626158</v>
       </c>
       <c r="F7" s="19">
-        <v>5.5268986480760711</v>
+        <v>5.5194374243630824</v>
       </c>
       <c r="G7" s="19">
-        <v>5.361294854712356</v>
+        <v>5.3733352422480367</v>
       </c>
       <c r="H7" s="19">
-        <v>5.1735285113718614</v>
+        <v>5.1909048534167033</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -1884,160 +2085,238 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>9.9087365286860907E-2</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.12863110193428445</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.16181997538778869</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.18891863469549727</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.22454563348640194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>7.934390424474784E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>0.10457402630622066</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.13210913910203753</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.15508263057694635</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.18376846484655879</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>9.4122689901427886E-2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>0.12218616656108658</v>
+      </c>
+      <c r="F12" s="23">
+        <v>0.15371214401742869</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0.17945305154261959</v>
+      </c>
+      <c r="H12" s="24">
+        <v>0.21329499445438171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>0.10707934533505734</v>
+      </c>
+      <c r="E13" s="25">
+        <v>0.14112890438791845</v>
+      </c>
+      <c r="F13" s="25">
+        <v>0.17828918632726104</v>
+      </c>
+      <c r="G13" s="25">
+        <v>0.20929328740609843</v>
+      </c>
+      <c r="H13" s="26">
+        <v>0.24800653681345139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="20" t="s">
+      <c r="C15" s="27">
+        <v>179.4950246699739</v>
+      </c>
+      <c r="D15" s="27">
+        <v>161.70933559332613</v>
+      </c>
+      <c r="E15" s="27">
+        <v>156.40638185495359</v>
+      </c>
+      <c r="F15" s="27">
+        <v>150.44914419564822</v>
+      </c>
+      <c r="G15" s="27">
+        <v>145.58506967468784</v>
+      </c>
+      <c r="H15" s="27">
+        <v>139.1902006477973</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>0.11037003084447812</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.15044412856073702</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.19330365774088398</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.23194483837830435</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0.27841189388628423</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>7.2032548385934661E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>9.9763926814357681E-2</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.12847793468310151</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.1545915599197247</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.18419993918719582</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A11" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>7.548127585160351E-2</v>
-      </c>
-      <c r="E12" s="21">
-        <v>0.10288766507774538</v>
-      </c>
-      <c r="F12" s="21">
-        <v>0.13219899098898913</v>
-      </c>
-      <c r="G12" s="21">
-        <v>0.15862541845854972</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0.19040390586109338</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>9.6938062402226674E-2</v>
-      </c>
-      <c r="E13" s="23">
-        <v>0.13425766517667392</v>
-      </c>
-      <c r="F13" s="23">
-        <v>0.17289964507283193</v>
-      </c>
-      <c r="G13" s="23">
-        <v>0.20804215064091802</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0.24788773408024212</v>
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>255.01663222562598</v>
+      </c>
+      <c r="D16" s="27">
+        <v>234.78261697749781</v>
+      </c>
+      <c r="E16" s="27">
+        <v>228.34851621873958</v>
+      </c>
+      <c r="F16" s="27">
+        <v>221.32660448559761</v>
+      </c>
+      <c r="G16" s="27">
+        <v>215.46798205920226</v>
+      </c>
+      <c r="H16" s="27">
+        <v>208.15261721118321</v>
       </c>
     </row>
   </sheetData>
@@ -2053,30 +2332,30 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -2090,30 +2369,30 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -2121,30 +2400,30 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>27</v>
+    <row r="6" spans="1:13" s="9" customFormat="1" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C6" s="19">
-        <v>140.40907171619028</v>
+        <v>145.23327758806684</v>
       </c>
       <c r="D6" s="19">
-        <v>127.19021927089229</v>
+        <v>131.61999682703831</v>
       </c>
       <c r="E6" s="19">
-        <v>122.16641687679852</v>
+        <v>126.45159833370846</v>
       </c>
       <c r="F6" s="19">
-        <v>117.30327552564326</v>
+        <v>121.45743230581094</v>
       </c>
       <c r="G6" s="19">
-        <v>112.99086856761856</v>
+        <v>117.03425926882902</v>
       </c>
       <c r="H6" s="19">
-        <v>107.42554692070965</v>
+        <v>111.31235131833476</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -2152,30 +2431,30 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>29</v>
+    <row r="7" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" s="19">
-        <v>253.198421247455</v>
+        <v>260.59287402119224</v>
       </c>
       <c r="D7" s="19">
-        <v>238.26054163008004</v>
+        <v>245.22139284804584</v>
       </c>
       <c r="E7" s="19">
-        <v>232.50788754040187</v>
+        <v>239.30753356598339</v>
       </c>
       <c r="F7" s="19">
-        <v>227.00927063064523</v>
+        <v>233.6634107443989</v>
       </c>
       <c r="G7" s="19">
-        <v>222.1598960190646</v>
+        <v>228.6910336197148</v>
       </c>
       <c r="H7" s="19">
-        <v>216.16162945156182</v>
+        <v>222.52631478747458</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -2183,30 +2462,30 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="E8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="F8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="G8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="H8" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -2214,30 +2493,30 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>9.414528764934324E-2</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.12992504413294428</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.16456056512680969</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.19527372991961875</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0.23491021194236247</v>
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>9.3733894787120575E-2</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.12932076977309492</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.16370797159651415</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.19416361585683037</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.23356166598363134</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -2245,108 +2524,186 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:13" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:13" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>5.8986575250313054E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>8.1680439402490576E-2</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.10333921592423649</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.12242023317522906</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.14607674663667886</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>5.4229130725072378E-2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>7.4817684098364839E-2</v>
+      </c>
+      <c r="F12" s="23">
+        <v>9.4712174423201706E-2</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0.11233208787777337</v>
+      </c>
+      <c r="H12" s="24">
+        <v>0.13512557165961669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>6.1233003021790702E-2</v>
+      </c>
+      <c r="E13" s="25">
+        <v>8.479113377119403E-2</v>
+      </c>
+      <c r="F13" s="25">
+        <v>0.10727475691046619</v>
+      </c>
+      <c r="G13" s="25">
+        <v>0.12708245013609837</v>
+      </c>
+      <c r="H13" s="26">
+        <v>0.15163989145427864</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>5.8996732853937993E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>8.1716677399153032E-2</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.10343330929071899</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.12258577709714838</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.14627576117347316</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A11" s="13" t="s">
+      <c r="B14" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="E14" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="F14" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="G14" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="H14" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="14" t="s">
+    </row>
+    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="B15" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="27">
+        <v>96.327899940553536</v>
+      </c>
+      <c r="D15" s="27">
+        <v>87.29871070246142</v>
+      </c>
+      <c r="E15" s="27">
+        <v>83.870701769615494</v>
+      </c>
+      <c r="F15" s="27">
+        <v>80.558254833133546</v>
+      </c>
+      <c r="G15" s="27">
+        <v>77.624526580200722</v>
+      </c>
+      <c r="H15" s="27">
+        <v>73.829395149733315</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>5.265790736819765E-2</v>
-      </c>
-      <c r="E12" s="21">
-        <v>7.2670455522361982E-2</v>
-      </c>
-      <c r="F12" s="21">
-        <v>9.2043003014461056E-2</v>
-      </c>
-      <c r="G12" s="21">
-        <v>0.10922167469336383</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0.13139138972497361</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>5.9505731259509941E-2</v>
-      </c>
-      <c r="E13" s="23">
-        <v>8.2421693702475832E-2</v>
-      </c>
-      <c r="F13" s="23">
-        <v>0.10432568734226887</v>
-      </c>
-      <c r="G13" s="23">
-        <v>0.12364339439339297</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0.14753776545081934</v>
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>172.84168415680804</v>
+      </c>
+      <c r="D16" s="27">
+        <v>162.64634514790168</v>
+      </c>
+      <c r="E16" s="27">
+        <v>158.72389944781349</v>
+      </c>
+      <c r="F16" s="27">
+        <v>154.98036003701901</v>
+      </c>
+      <c r="G16" s="27">
+        <v>151.68236487993229</v>
+      </c>
+      <c r="H16" s="27">
+        <v>147.59353325197716</v>
       </c>
     </row>
   </sheetData>
@@ -2362,30 +2719,30 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -2399,30 +2756,30 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -2430,30 +2787,30 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>28</v>
+    <row r="6" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>33</v>
       </c>
       <c r="C6" s="19">
-        <v>3.0427463999242614</v>
+        <v>3.6395966975772129</v>
       </c>
       <c r="D6" s="19">
-        <v>2.7378614675508404</v>
+        <v>3.2799751989526484</v>
       </c>
       <c r="E6" s="19">
-        <v>2.650134455661683</v>
+        <v>3.1792828539215874</v>
       </c>
       <c r="F6" s="19">
-        <v>2.5478613923148172</v>
+        <v>3.0612874757017363</v>
       </c>
       <c r="G6" s="19">
-        <v>2.4667990522878438</v>
+        <v>2.9688964173844075</v>
       </c>
       <c r="H6" s="19">
-        <v>2.3588081154579745</v>
+        <v>2.8443386095505518</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -2461,30 +2818,30 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>28</v>
+    <row r="7" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>33</v>
       </c>
       <c r="C7" s="19">
-        <v>4.4155744542833162</v>
+        <v>5.0345593631579062</v>
       </c>
       <c r="D7" s="19">
-        <v>4.0826504550271752</v>
+        <v>4.6464467134711818</v>
       </c>
       <c r="E7" s="19">
-        <v>3.982318178092854</v>
+        <v>4.5329458640743185</v>
       </c>
       <c r="F7" s="19">
-        <v>3.868450541640418</v>
+        <v>4.4031689691858222</v>
       </c>
       <c r="G7" s="19">
-        <v>3.7768598660802626</v>
+        <v>4.3000798231124486</v>
       </c>
       <c r="H7" s="19">
-        <v>3.659466523115622</v>
+        <v>4.1659680106944155</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -2492,30 +2849,30 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="E8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="F8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="G8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="H8" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -2523,30 +2880,30 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>0.1002005728709465</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.12903209556746204</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.16264418474762229</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.18928535997964005</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0.22477663090269737</v>
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>9.880806268011931E-2</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.12647386012907549</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.15889376486698165</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.18427873633341674</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.21850170612475942</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -2554,30 +2911,30 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>7.5397664041920748E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>9.8120025078545114E-2</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.12390775386250413</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.14465039482766964</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.17123659424069584</v>
+    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>7.7089695778913683E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>9.9634042008584583E-2</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.12541125219269378</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.14588755183229349</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.17252579417767963</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -2585,30 +2942,30 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="E11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="F11" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="G11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="H11" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
@@ -2616,56 +2973,134 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="1:13" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:13" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>2.4737087688970399E-2</v>
-      </c>
-      <c r="E12" s="21">
-        <v>3.1854890359308649E-2</v>
-      </c>
-      <c r="F12" s="21">
-        <v>4.0152898780178706E-2</v>
-      </c>
-      <c r="G12" s="21">
-        <v>4.6729957862470001E-2</v>
-      </c>
-      <c r="H12" s="22">
-        <v>5.5491890612569469E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>2.9178183641489542E-2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>3.7347939192382627E-2</v>
+      </c>
+      <c r="F12" s="23">
+        <v>4.6921590455485003E-2</v>
+      </c>
+      <c r="G12" s="23">
+        <v>5.4417814337330672E-2</v>
+      </c>
+      <c r="H12" s="24">
+        <v>6.4523913680272882E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>3.1489836423730461E-2</v>
+      </c>
+      <c r="E13" s="25">
+        <v>4.0698820424500952E-2</v>
+      </c>
+      <c r="F13" s="25">
+        <v>5.1228374652937107E-2</v>
+      </c>
+      <c r="G13" s="25">
+        <v>5.9592596611517681E-2</v>
+      </c>
+      <c r="H13" s="26">
+        <v>7.0473867909793389E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>2.7012060252538175E-2</v>
-      </c>
-      <c r="E13" s="23">
-        <v>3.5152601384687385E-2</v>
-      </c>
-      <c r="F13" s="23">
-        <v>4.4391344952407451E-2</v>
-      </c>
-      <c r="G13" s="23">
-        <v>5.1822629126361333E-2</v>
-      </c>
-      <c r="H13" s="24">
-        <v>6.1347433767939774E-2</v>
+      <c r="B14" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="27">
+        <v>198.06241303997606</v>
+      </c>
+      <c r="D15" s="27">
+        <v>178.4922497177464</v>
+      </c>
+      <c r="E15" s="27">
+        <v>173.01269511633095</v>
+      </c>
+      <c r="F15" s="27">
+        <v>166.59153055341508</v>
+      </c>
+      <c r="G15" s="27">
+        <v>161.56372184982206</v>
+      </c>
+      <c r="H15" s="27">
+        <v>154.78543787155451</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>273.97457985491695</v>
+      </c>
+      <c r="D16" s="27">
+        <v>252.85396284274569</v>
+      </c>
+      <c r="E16" s="27">
+        <v>246.67738505636791</v>
+      </c>
+      <c r="F16" s="27">
+        <v>239.61508472634463</v>
+      </c>
+      <c r="G16" s="27">
+        <v>234.00509913560188</v>
+      </c>
+      <c r="H16" s="27">
+        <v>226.70689788095129</v>
       </c>
     </row>
   </sheetData>
@@ -2682,9 +3117,9 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:M20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="27.6640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="27.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
@@ -2692,20 +3127,20 @@
     <col min="13" max="16384" width="27.6640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -2719,30 +3154,30 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -2750,30 +3185,30 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>27</v>
+    <row r="6" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C6" s="19">
-        <v>4.1694474064920435</v>
+        <v>3.4669512983264461</v>
       </c>
       <c r="D6" s="19">
-        <v>3.7638153286651304</v>
+        <v>3.1331081983759899</v>
       </c>
       <c r="E6" s="19">
-        <v>3.6210331656650392</v>
+        <v>3.007229035921744</v>
       </c>
       <c r="F6" s="19">
-        <v>3.4721890277391472</v>
+        <v>2.8808800977279088</v>
       </c>
       <c r="G6" s="19">
-        <v>3.3440439860371387</v>
+        <v>2.7687119547349606</v>
       </c>
       <c r="H6" s="19">
-        <v>3.1797580098656613</v>
+        <v>2.6270596352774489</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -2781,30 +3216,30 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>29</v>
+    <row r="7" spans="1:13" s="9" customFormat="1" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" s="19">
-        <v>7.4278510666728543</v>
+        <v>6.7690737531714058</v>
       </c>
       <c r="D7" s="19">
-        <v>6.9573061266919796</v>
+        <v>6.3694468394024524</v>
       </c>
       <c r="E7" s="19">
-        <v>6.7855170418398219</v>
+        <v>6.2141715621683922</v>
       </c>
       <c r="F7" s="19">
-        <v>6.6101311373170821</v>
+        <v>6.060924740037783</v>
       </c>
       <c r="G7" s="19">
-        <v>6.4580449643373701</v>
+        <v>5.9244942417840063</v>
       </c>
       <c r="H7" s="19">
-        <v>6.2725640851549516</v>
+        <v>5.7613626421452251</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -2812,30 +3247,30 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="E8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="F8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="G8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="H8" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -2843,30 +3278,30 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>9.72867716703473E-2</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.13153163653607794</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.16723040508131348</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.19796470370862798</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0.23736704175363504</v>
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>9.6292988053108139E-2</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.13260130381024318</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.16904512067459485</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.20139865937215129</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.24225655072063648</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -2874,30 +3309,30 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>29</v>
+    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>6.3348731114454784E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>8.6476427578771067E-2</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.11008835826349601</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.13056348244336677</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.15553448381610976</v>
+        <v>27</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>5.9037163479231207E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>8.197608878807594E-2</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.10461534900574027</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.12477032193536113</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.14886986724794571</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -2905,103 +3340,172 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="E11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="F11" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="G11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="H11" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="14" t="s">
+    </row>
+    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="B12" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>4.6770324454475688E-2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>6.4405582666840877E-2</v>
+      </c>
+      <c r="F12" s="23">
+        <v>8.2106654921085889E-2</v>
+      </c>
+      <c r="G12" s="23">
+        <v>9.7821044231557672E-2</v>
+      </c>
+      <c r="H12" s="24">
+        <v>0.11766607005878027</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+      <c r="B13" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>5.6827725035872599E-2</v>
-      </c>
-      <c r="E12" s="21">
-        <v>7.6831038241438734E-2</v>
-      </c>
-      <c r="F12" s="21">
-        <v>9.7683614271836902E-2</v>
-      </c>
-      <c r="G12" s="21">
-        <v>0.11563631474258108</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0.13865224171546311</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>5.5986421227482333E-2</v>
+      </c>
+      <c r="E13" s="25">
+        <v>7.7739978803102169E-2</v>
+      </c>
+      <c r="F13" s="25">
+        <v>9.9209356465032553E-2</v>
+      </c>
+      <c r="G13" s="25">
+        <v>0.11832282225109153</v>
+      </c>
+      <c r="H13" s="26">
+        <v>0.14117702485409789</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>6.5921804334381384E-2</v>
-      </c>
-      <c r="E13" s="23">
-        <v>8.9988892249228944E-2</v>
-      </c>
-      <c r="F13" s="23">
-        <v>0.1145598828148197</v>
-      </c>
-      <c r="G13" s="23">
-        <v>0.13586665733361689</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0.16185192077249139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A14" s="6"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A15" s="6"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A16" s="6"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="B14" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="27">
+        <v>78.859056276455618</v>
+      </c>
+      <c r="D15" s="27">
+        <v>71.265482112547488</v>
+      </c>
+      <c r="E15" s="27">
+        <v>68.402242596952249</v>
+      </c>
+      <c r="F15" s="27">
+        <v>65.528317591917514</v>
+      </c>
+      <c r="G15" s="27">
+        <v>62.976948063024423</v>
+      </c>
+      <c r="H15" s="27">
+        <v>59.754933309836915</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>153.96892604130261</v>
+      </c>
+      <c r="D16" s="27">
+        <v>144.87903738388053</v>
+      </c>
+      <c r="E16" s="27">
+        <v>141.34715568953607</v>
+      </c>
+      <c r="F16" s="27">
+        <v>137.86141310745268</v>
+      </c>
+      <c r="G16" s="27">
+        <v>134.75817357108741</v>
+      </c>
+      <c r="H16" s="27">
+        <v>131.04759246122509</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
     </row>
   </sheetData>
@@ -3017,30 +3521,30 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -3054,30 +3558,30 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -3085,30 +3589,30 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>28</v>
+    <row r="6" spans="1:13" s="9" customFormat="1" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>33</v>
       </c>
       <c r="C6" s="19">
-        <v>16.391280732449708</v>
+        <v>12.521360165363163</v>
       </c>
       <c r="D6" s="19">
-        <v>14.810457460052758</v>
+        <v>11.378785447689744</v>
       </c>
       <c r="E6" s="19">
-        <v>14.348707712228107</v>
+        <v>10.9893914287959</v>
       </c>
       <c r="F6" s="19">
-        <v>13.826949582633098</v>
+        <v>10.595180215454352</v>
       </c>
       <c r="G6" s="19">
-        <v>13.409414817105107</v>
+        <v>10.259859444733616</v>
       </c>
       <c r="H6" s="19">
-        <v>12.849809111408907</v>
+        <v>9.816399816870911</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -3116,30 +3620,30 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>28</v>
+    <row r="7" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>33</v>
       </c>
       <c r="C7" s="19">
-        <v>23.634637500731014</v>
+        <v>20.773638498738407</v>
       </c>
       <c r="D7" s="19">
-        <v>21.911217043928691</v>
+        <v>19.468604345072304</v>
       </c>
       <c r="E7" s="19">
-        <v>21.385630709450581</v>
+        <v>19.006481990716118</v>
       </c>
       <c r="F7" s="19">
-        <v>20.805368636484022</v>
+        <v>18.545617864954714</v>
       </c>
       <c r="G7" s="19">
-        <v>20.33495564240873</v>
+        <v>18.150053498107525</v>
       </c>
       <c r="H7" s="19">
-        <v>19.728412370801532</v>
+        <v>17.653118407061097</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -3147,30 +3651,30 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="E8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="F8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="G8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="H8" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -3178,30 +3682,30 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>9.6442938059587063E-2</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.1246133876639629</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.1564448313510988</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.18191781130570359</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0.21605826163600342</v>
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>9.1250048124486685E-2</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.12234842831252676</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.15383152664492858</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.18061142645551842</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.21602767692720534</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -3209,108 +3713,186 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:13" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:13" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>6.2821645507375054E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>8.5067260033893879E-2</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.10725230603772189</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.12629395667928919</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.15021538436161874</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>7.5425816408239282E-2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>0.10113123534080526</v>
+      </c>
+      <c r="F12" s="23">
+        <v>0.12715465607963833</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0.14929048886066851</v>
+      </c>
+      <c r="H12" s="24">
+        <v>0.17856498965108331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>8.6150397832482489E-2</v>
+      </c>
+      <c r="E13" s="25">
+        <v>0.11665689803650313</v>
+      </c>
+      <c r="F13" s="25">
+        <v>0.14708033766030815</v>
+      </c>
+      <c r="G13" s="25">
+        <v>0.17319308534320013</v>
+      </c>
+      <c r="H13" s="26">
+        <v>0.20599771016493795</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>7.2919267610895996E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>9.5157236543647924E-2</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.11970857873997359</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.13961212048292365</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.165275440751256</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A11" s="13" t="s">
+      <c r="B14" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="E14" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="F14" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="G14" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="H14" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="14" t="s">
+    </row>
+    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="B15" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="27">
+        <v>115.18317041958437</v>
+      </c>
+      <c r="D15" s="27">
+        <v>104.67270057566634</v>
+      </c>
+      <c r="E15" s="27">
+        <v>101.09069055069432</v>
+      </c>
+      <c r="F15" s="27">
+        <v>97.46436747013675</v>
+      </c>
+      <c r="G15" s="27">
+        <v>94.379773706434179</v>
+      </c>
+      <c r="H15" s="27">
+        <v>90.300417692731173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="31" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>0.10435631392271465</v>
-      </c>
-      <c r="E12" s="21">
-        <v>0.1348382169153623</v>
-      </c>
-      <c r="F12" s="21">
-        <v>0.16928150739222014</v>
-      </c>
-      <c r="G12" s="21">
-        <v>0.19684460683914234</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0.23378636352774887</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>0.11376971060034509</v>
-      </c>
-      <c r="E13" s="23">
-        <v>0.14846571582243542</v>
-      </c>
-      <c r="F13" s="23">
-        <v>0.18677107993320494</v>
-      </c>
-      <c r="G13" s="23">
-        <v>0.21782487762218439</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0.25786516622672684</v>
+      <c r="B16" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>191.09533723452529</v>
+      </c>
+      <c r="D16" s="27">
+        <v>179.09041370066564</v>
+      </c>
+      <c r="E16" s="27">
+        <v>174.83938049073129</v>
+      </c>
+      <c r="F16" s="27">
+        <v>170.5999216430663</v>
+      </c>
+      <c r="G16" s="27">
+        <v>166.96115099221399</v>
+      </c>
+      <c r="H16" s="27">
+        <v>162.38987770212793</v>
       </c>
     </row>
   </sheetData>
@@ -3327,29 +3909,29 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:M24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4"/>
       <c r="B4"/>
       <c r="C4"/>
@@ -3364,30 +3946,30 @@
       <c r="L4"/>
       <c r="M4"/>
     </row>
-    <row r="5" spans="1:13" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -3395,30 +3977,30 @@
       <c r="L5"/>
       <c r="M5"/>
     </row>
-    <row r="6" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>28</v>
+    <row r="6" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>33</v>
       </c>
       <c r="C6" s="19">
-        <v>3.7654210252182669</v>
+        <v>3.9570855795902284</v>
       </c>
       <c r="D6" s="19">
-        <v>3.4245878623045418</v>
+        <v>3.6183853624862166</v>
       </c>
       <c r="E6" s="19">
-        <v>3.3092991382540569</v>
+        <v>3.4977324963788115</v>
       </c>
       <c r="F6" s="19">
-        <v>3.1933350117705608</v>
+        <v>3.3831450501897113</v>
       </c>
       <c r="G6" s="19">
-        <v>3.0958797663665636</v>
+        <v>3.2864801063866662</v>
       </c>
       <c r="H6" s="19">
-        <v>2.9648137936882333</v>
+        <v>3.153093033048906</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -3426,30 +4008,30 @@
       <c r="L6"/>
       <c r="M6"/>
     </row>
-    <row r="7" spans="1:13" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>28</v>
+    <row r="7" spans="1:13" s="9" customFormat="1" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>33</v>
       </c>
       <c r="C7" s="19">
-        <v>6.0448383680708311</v>
+        <v>6.3204417067818319</v>
       </c>
       <c r="D7" s="19">
-        <v>5.6496931096622447</v>
+        <v>5.9254293693586151</v>
       </c>
       <c r="E7" s="19">
-        <v>5.5095967447586531</v>
+        <v>5.7790553292875204</v>
       </c>
       <c r="F7" s="19">
-        <v>5.3705032415516563</v>
+        <v>5.6404867747818548</v>
       </c>
       <c r="G7" s="19">
-        <v>5.2516891176356149</v>
+        <v>5.5216764188805527</v>
       </c>
       <c r="H7" s="19">
-        <v>5.1011338835340867</v>
+        <v>5.3680823985598813</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -3457,30 +4039,30 @@
       <c r="L7"/>
       <c r="M7"/>
     </row>
-    <row r="8" spans="1:13" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="E8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="F8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="G8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="H8" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -3488,30 +4070,30 @@
       <c r="L8"/>
       <c r="M8"/>
     </row>
-    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>9.051661437885776E-2</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.12113436556215396</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.15193148644368248</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.17781311953366294</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0.21262090644528273</v>
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>8.5593351544114349E-2</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.11608368683777236</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.14504122234827957</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.16946954007322884</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.20317795265488775</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -3519,30 +4101,30 @@
       <c r="L9"/>
       <c r="M9"/>
     </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>6.5369036250127938E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>8.8545233258734202E-2</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.11155552646056677</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.13121099393238936</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.15611740580549571</v>
+    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>6.2497584148172546E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>8.5656414948563506E-2</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.107580286876214</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.12637808003896378</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.15067923294032906</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -3550,30 +4132,30 @@
       <c r="L10"/>
       <c r="M10"/>
     </row>
-    <row r="11" spans="1:13" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:13" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="E11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="F11" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="G11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="H11" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -3581,104 +4163,152 @@
       <c r="L11"/>
       <c r="M11"/>
     </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>2.5457835797254729E-2</v>
-      </c>
-      <c r="E12" s="21">
-        <v>3.4069091172352114E-2</v>
-      </c>
-      <c r="F12" s="21">
-        <v>4.273079435038532E-2</v>
-      </c>
-      <c r="G12" s="21">
-        <v>5.0010014523288911E-2</v>
-      </c>
-      <c r="H12" s="22">
-        <v>5.9799719206154567E-2</v>
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>2.5298519773767111E-2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>3.4310438765370585E-2</v>
+      </c>
+      <c r="F12" s="23">
+        <v>4.2869313625348009E-2</v>
+      </c>
+      <c r="G12" s="23">
+        <v>5.0089503837037301E-2</v>
+      </c>
+      <c r="H12" s="24">
+        <v>6.0052578384946348E-2</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
     </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>2.9514566653761759E-2</v>
-      </c>
-      <c r="E13" s="23">
-        <v>3.9978778008719351E-2</v>
-      </c>
-      <c r="F13" s="23">
-        <v>5.0368082660992838E-2</v>
-      </c>
-      <c r="G13" s="23">
-        <v>5.9242660566473565E-2</v>
-      </c>
-      <c r="H13" s="24">
-        <v>7.0488075758492738E-2</v>
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>2.9504638392701073E-2</v>
+      </c>
+      <c r="E13" s="25">
+        <v>4.0437747850873028E-2</v>
+      </c>
+      <c r="F13" s="25">
+        <v>5.078784253388699E-2</v>
+      </c>
+      <c r="G13" s="25">
+        <v>5.9662138995215698E-2</v>
+      </c>
+      <c r="H13" s="26">
+        <v>7.1134530106856553E-2</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
     </row>
-    <row r="14" spans="1:13" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14"/>
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
+    <row r="14" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>24</v>
+      </c>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
     </row>
-    <row r="15" spans="1:13" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15"/>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
+    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="27">
+        <v>128.7215566895689</v>
+      </c>
+      <c r="D15" s="27">
+        <v>117.70384723653298</v>
+      </c>
+      <c r="E15" s="27">
+        <v>113.77908381354642</v>
+      </c>
+      <c r="F15" s="27">
+        <v>110.05162476474045</v>
+      </c>
+      <c r="G15" s="27">
+        <v>106.90717367987762</v>
+      </c>
+      <c r="H15" s="27">
+        <v>102.56817433883222</v>
+      </c>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
     </row>
-    <row r="16" spans="1:13" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16"/>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>205.60007588890261</v>
+      </c>
+      <c r="D16" s="27">
+        <v>192.75056784516528</v>
+      </c>
+      <c r="E16" s="27">
+        <v>187.98911047510666</v>
+      </c>
+      <c r="F16" s="27">
+        <v>183.48156074300312</v>
+      </c>
+      <c r="G16" s="27">
+        <v>179.61673304219789</v>
+      </c>
+      <c r="H16" s="27">
+        <v>174.62041416148929</v>
+      </c>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
     </row>
-    <row r="17" spans="2:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -3690,31 +4320,31 @@
       <c r="J17"/>
       <c r="K17"/>
     </row>
-    <row r="18" spans="2:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J18"/>
       <c r="K18"/>
     </row>
-    <row r="19" spans="2:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J19"/>
       <c r="K19"/>
     </row>
-    <row r="20" spans="2:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J20"/>
       <c r="K20"/>
     </row>
-    <row r="21" spans="2:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J21"/>
       <c r="K21"/>
     </row>
-    <row r="22" spans="2:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J22"/>
       <c r="K22"/>
     </row>
-    <row r="23" spans="2:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J23"/>
       <c r="K23"/>
     </row>
-    <row r="24" spans="2:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J24"/>
       <c r="K24"/>
     </row>
@@ -3731,27 +4361,27 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="8" width="14.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A2" s="16"/>
-    </row>
-    <row r="3" spans="1:14" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="12"/>
+    </row>
+    <row r="3" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B3"/>
@@ -3762,163 +4392,163 @@
       <c r="G3"/>
       <c r="H3"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A5" s="25" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="19">
+        <v>45.645588371172607</v>
+      </c>
+      <c r="D6" s="19">
+        <v>41.340236997145645</v>
+      </c>
+      <c r="E6" s="19">
+        <v>39.978903552285878</v>
+      </c>
+      <c r="F6" s="19">
+        <v>38.522402514226641</v>
+      </c>
+      <c r="G6" s="19">
+        <v>37.337709660547851</v>
+      </c>
+      <c r="H6" s="19">
+        <v>35.737938918310142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="19">
+        <v>68.074555139972617</v>
+      </c>
+      <c r="D7" s="19">
+        <v>63.23478465712477</v>
+      </c>
+      <c r="E7" s="19">
+        <v>61.629349466680154</v>
+      </c>
+      <c r="F7" s="19">
+        <v>59.945260434021726</v>
+      </c>
+      <c r="G7" s="19">
+        <v>58.550400899867483</v>
+      </c>
+      <c r="H7" s="19">
+        <v>56.758860099294459</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="26" t="s">
+      <c r="B8" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="F8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="G8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="H8" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="26" t="s">
+    </row>
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="B9" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>9.432130305819432E-2</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.12414529029196421</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.15605420175599274</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.18200836065619833</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.21705601365672447</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="31" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="B10" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="19">
-        <v>45.370865162272679</v>
-      </c>
-      <c r="D6" s="19">
-        <v>41.059360141546506</v>
-      </c>
-      <c r="E6" s="19">
-        <v>39.681405458492549</v>
-      </c>
-      <c r="F6" s="19">
-        <v>38.208367729983934</v>
-      </c>
-      <c r="G6" s="19">
-        <v>37.001726798888924</v>
-      </c>
-      <c r="H6" s="19">
-        <v>35.384669547870054</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="19">
-        <v>69.263732264717675</v>
-      </c>
-      <c r="D7" s="19">
-        <v>64.382927513170813</v>
-      </c>
-      <c r="E7" s="19">
-        <v>62.744938980726765</v>
-      </c>
-      <c r="F7" s="19">
-        <v>61.029458978121298</v>
-      </c>
-      <c r="G7" s="19">
-        <v>59.59893414645591</v>
-      </c>
-      <c r="H7" s="19">
-        <v>57.777590333097159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A8" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>9.5028053913138233E-2</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.12539896877503445</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.15786556872282415</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.18446062982160102</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0.22010150299506445</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>7.0466961452394908E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>9.4115535949995638E-2</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.11888289899143714</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.1395362017357665</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.16583198098135774</v>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>7.1095146679937507E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>9.4678630804711797E-2</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.11941752229207679</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.13990769709066606</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.16622503103268474</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
@@ -3927,82 +4557,160 @@
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A11" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="14" t="s">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="B11" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="F11" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="G11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="H11" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="14" t="s">
+    </row>
+    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="B12" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>2.6536894940479058E-2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>3.4927746108432495E-2</v>
+      </c>
+      <c r="F12" s="23">
+        <v>4.3905181785540738E-2</v>
+      </c>
+      <c r="G12" s="23">
+        <v>5.1207273313881002E-2</v>
+      </c>
+      <c r="H12" s="24">
+        <v>6.1067780489142375E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+      <c r="B13" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>2.6574824173605748E-2</v>
-      </c>
-      <c r="E12" s="21">
-        <v>3.5068123670027984E-2</v>
-      </c>
-      <c r="F12" s="21">
-        <v>4.4147486548657043E-2</v>
-      </c>
-      <c r="G12" s="21">
-        <v>5.1584859445215792E-2</v>
-      </c>
-      <c r="H12" s="22">
-        <v>6.1551915477367394E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" s="10" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>2.9830894085477865E-2</v>
+      </c>
+      <c r="E13" s="25">
+        <v>3.9726315221042065E-2</v>
+      </c>
+      <c r="F13" s="25">
+        <v>5.0106535056216386E-2</v>
+      </c>
+      <c r="G13" s="25">
+        <v>5.8704030986021276E-2</v>
+      </c>
+      <c r="H13" s="26">
+        <v>6.9746551299971926E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>3.008381701390464E-2</v>
-      </c>
-      <c r="E13" s="23">
-        <v>4.0179887188665005E-2</v>
-      </c>
-      <c r="F13" s="23">
-        <v>5.0753591550233554E-2</v>
-      </c>
-      <c r="G13" s="23">
-        <v>5.9570917679911052E-2</v>
-      </c>
-      <c r="H13" s="24">
-        <v>7.0797134828451277E-2</v>
+      <c r="B14" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="27">
+        <v>156.45683896770177</v>
+      </c>
+      <c r="D15" s="27">
+        <v>141.69962604390207</v>
+      </c>
+      <c r="E15" s="27">
+        <v>137.03345927589334</v>
+      </c>
+      <c r="F15" s="27">
+        <v>132.04109185333115</v>
+      </c>
+      <c r="G15" s="27">
+        <v>127.98038619373956</v>
+      </c>
+      <c r="H15" s="27">
+        <v>122.49694119204035</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>233.33535816703548</v>
+      </c>
+      <c r="D16" s="27">
+        <v>216.74634665253438</v>
+      </c>
+      <c r="E16" s="27">
+        <v>211.24348593745356</v>
+      </c>
+      <c r="F16" s="27">
+        <v>205.4710278315938</v>
+      </c>
+      <c r="G16" s="27">
+        <v>200.68994555605983</v>
+      </c>
+      <c r="H16" s="27">
+        <v>194.54918101469741</v>
       </c>
     </row>
   </sheetData>
@@ -4018,30 +4726,30 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4055,238 +4763,316 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="14" t="s">
+    </row>
+    <row r="6" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="B6" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="19">
+        <v>9.003374838997015</v>
+      </c>
+      <c r="D6" s="19">
+        <v>8.1195523247414005</v>
+      </c>
+      <c r="E6" s="19">
+        <v>7.8109733155120917</v>
+      </c>
+      <c r="F6" s="19">
+        <v>7.499229433283352</v>
+      </c>
+      <c r="G6" s="19">
+        <v>7.2455086674805855</v>
+      </c>
+      <c r="H6" s="19">
+        <v>6.8949473374931332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="B7" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="19">
+        <v>14.6508372027024</v>
+      </c>
+      <c r="D7" s="19">
+        <v>13.565481105851617</v>
+      </c>
+      <c r="E7" s="19">
+        <v>13.157356838101226</v>
+      </c>
+      <c r="F7" s="19">
+        <v>12.75112885266083</v>
+      </c>
+      <c r="G7" s="19">
+        <v>12.408263290055439</v>
+      </c>
+      <c r="H7" s="19">
+        <v>11.97419538331005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="19">
-        <v>8.8064510909906701</v>
-      </c>
-      <c r="D6" s="19">
-        <v>7.8629891439171873</v>
-      </c>
-      <c r="E6" s="19">
-        <v>7.5506447544715787</v>
-      </c>
-      <c r="F6" s="19">
-        <v>7.2104884080665714</v>
-      </c>
-      <c r="G6" s="19">
-        <v>6.9863583811410033</v>
-      </c>
-      <c r="H6" s="19">
-        <v>6.6172653441106446</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>9.816569120586266E-2</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.13243939576081873</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.16706462105727748</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.19524525002585114</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.23418190836301589</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>7.4081506867783961E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>0.1019382267332611</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.12966551492983358</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.15306797022038507</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.18269548575003164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>4.6207724880625932E-2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>6.2340753551448178E-2</v>
+      </c>
+      <c r="F12" s="23">
+        <v>7.8639247096134832E-2</v>
+      </c>
+      <c r="G12" s="23">
+        <v>9.1904194699998706E-2</v>
+      </c>
+      <c r="H12" s="24">
+        <v>0.11023212958349686</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>5.6744238930177673E-2</v>
+      </c>
+      <c r="E13" s="25">
+        <v>7.8081660841408662E-2</v>
+      </c>
+      <c r="F13" s="25">
+        <v>9.9319941929835301E-2</v>
+      </c>
+      <c r="G13" s="25">
+        <v>0.11724552917429977</v>
+      </c>
+      <c r="H13" s="26">
+        <v>0.13993932808854564</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="19">
-        <v>14.583960172296853</v>
-      </c>
-      <c r="D7" s="19">
-        <v>13.434323835976478</v>
-      </c>
-      <c r="E7" s="19">
-        <v>13.020141913481924</v>
-      </c>
-      <c r="F7" s="19">
-        <v>12.583325734892355</v>
-      </c>
-      <c r="G7" s="19">
-        <v>12.267998132859718</v>
-      </c>
-      <c r="H7" s="19">
-        <v>11.813475574657442</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A8" s="13" t="s">
+      <c r="B14" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="20" t="s">
+      <c r="C15" s="27">
+        <v>122.5623263763532</v>
+      </c>
+      <c r="D15" s="27">
+        <v>110.53091089181991</v>
+      </c>
+      <c r="E15" s="27">
+        <v>106.3302459280287</v>
+      </c>
+      <c r="F15" s="27">
+        <v>102.08649776438935</v>
+      </c>
+      <c r="G15" s="27">
+        <v>98.632614319252127</v>
+      </c>
+      <c r="H15" s="27">
+        <v>93.860446892127982</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>0.10713304795829501</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.14260072798267492</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.18122654250096595</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.20667720640743578</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0.24858887243689398</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>7.882881760087232E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>0.1072286429981824</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.13718046496073327</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.1588019997364262</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.18996792125791187</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A11" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>4.9325774556024465E-2</v>
-      </c>
-      <c r="E12" s="21">
-        <v>6.5655663626190894E-2</v>
-      </c>
-      <c r="F12" s="21">
-        <v>8.3439608499239953E-2</v>
-      </c>
-      <c r="G12" s="21">
-        <v>9.5157502595190388E-2</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0.11445430623547528</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>6.0104917768703678E-2</v>
-      </c>
-      <c r="E13" s="23">
-        <v>8.175904404005821E-2</v>
-      </c>
-      <c r="F13" s="23">
-        <v>0.10459652722034699</v>
-      </c>
-      <c r="G13" s="23">
-        <v>0.12108238365303069</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0.14484558608642656</v>
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>199.44084557568692</v>
+      </c>
+      <c r="D16" s="27">
+        <v>184.665967204455</v>
+      </c>
+      <c r="E16" s="27">
+        <v>179.11019943951919</v>
+      </c>
+      <c r="F16" s="27">
+        <v>173.58024563607404</v>
+      </c>
+      <c r="G16" s="27">
+        <v>168.91284016437925</v>
+      </c>
+      <c r="H16" s="27">
+        <v>163.00390341483973</v>
       </c>
     </row>
   </sheetData>
@@ -4302,26 +5088,26 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>5</v>
       </c>
       <c r="B3"/>
@@ -4332,7 +5118,7 @@
       <c r="G3"/>
       <c r="H3"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4346,30 +5132,30 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -4377,30 +5163,30 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>27</v>
+    <row r="6" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C6" s="19">
-        <v>15.304234603576999</v>
+        <v>25.283566277186448</v>
       </c>
       <c r="D6" s="19">
-        <v>13.935439901878814</v>
+        <v>23.140807685945216</v>
       </c>
       <c r="E6" s="19">
-        <v>13.444063956845302</v>
+        <v>22.459314851141528</v>
       </c>
       <c r="F6" s="19">
-        <v>12.955217908210496</v>
+        <v>21.775386159639346</v>
       </c>
       <c r="G6" s="19">
-        <v>12.527849882528777</v>
+        <v>21.219914299205389</v>
       </c>
       <c r="H6" s="19">
-        <v>11.974757285174629</v>
+        <v>20.441532345887335</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -4408,30 +5194,30 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>29</v>
+    <row r="7" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" s="19">
-        <v>27.450340207742745</v>
+        <v>36.017251303509205</v>
       </c>
       <c r="D7" s="19">
-        <v>25.945697234469201</v>
+        <v>33.754441676489058</v>
       </c>
       <c r="E7" s="19">
-        <v>25.397886573592928</v>
+        <v>33.023076686432688</v>
       </c>
       <c r="F7" s="19">
-        <v>24.860816601465793</v>
+        <v>32.296531832814928</v>
       </c>
       <c r="G7" s="19">
-        <v>24.393886693572707</v>
+        <v>31.706098578454046</v>
       </c>
       <c r="H7" s="19">
-        <v>23.81037918760958</v>
+        <v>30.900838540937457</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -4439,30 +5225,30 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="E8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="F8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="G8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="H8" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -4470,30 +5256,30 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:13" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:13" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>8.9438951842665954E-2</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.12154614032752263</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.1534880218588309</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.18141284376281769</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0.21755268425016069</v>
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>8.4749064580128472E-2</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.11170304833908118</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.13875337359795478</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.16072305360054065</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.19150913594290361</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -4501,30 +5287,30 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>29</v>
+    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>5.4813272326917788E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>7.4769697519846925E-2</v>
-      </c>
-      <c r="F10" s="21">
-        <v>9.4334845640512005E-2</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.11134483183228173</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.13260167242322421</v>
+        <v>27</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>6.2825716708695051E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>8.3131680200837291E-2</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.10330381514515415</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.1196968832720202</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.14205450381143467</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -4532,30 +5318,30 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="E11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="F11" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="G11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="H11" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
@@ -4563,30 +5349,30 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="1:13" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:13" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>4.8833420980902098E-2</v>
-      </c>
-      <c r="E12" s="21">
-        <v>6.6363857323138223E-2</v>
-      </c>
-      <c r="F12" s="21">
-        <v>8.3804036524750658E-2</v>
-      </c>
-      <c r="G12" s="21">
-        <v>9.9050912251256867E-2</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0.11878316546242627</v>
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>7.6445527014905271E-2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>0.10075861535178204</v>
+      </c>
+      <c r="F12" s="23">
+        <v>0.12515860584824426</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0.14497574217260553</v>
+      </c>
+      <c r="H12" s="24">
+        <v>0.17274546802204024</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
@@ -4594,30 +5380,108 @@
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
     </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>8.0728494184570523E-2</v>
+      </c>
+      <c r="E13" s="25">
+        <v>0.10682083250660404</v>
+      </c>
+      <c r="F13" s="25">
+        <v>0.13274120658038324</v>
+      </c>
+      <c r="G13" s="25">
+        <v>0.1538056332877322</v>
+      </c>
+      <c r="H13" s="26">
+        <v>0.18253426758355323</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>5.3679973811021228E-2</v>
-      </c>
-      <c r="E13" s="23">
-        <v>7.3223787494116441E-2</v>
-      </c>
-      <c r="F13" s="23">
-        <v>9.2384414001910095E-2</v>
-      </c>
-      <c r="G13" s="23">
-        <v>0.10904270814377666</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0.12986005032727715</v>
+      <c r="B14" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="27">
+        <v>176.90514433917929</v>
+      </c>
+      <c r="D15" s="27">
+        <v>161.91259883702128</v>
+      </c>
+      <c r="E15" s="27">
+        <v>157.14430044962779</v>
+      </c>
+      <c r="F15" s="27">
+        <v>152.35895875528504</v>
+      </c>
+      <c r="G15" s="27">
+        <v>148.47240934334195</v>
+      </c>
+      <c r="H15" s="27">
+        <v>143.02619300292844</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>252.00705354200628</v>
+      </c>
+      <c r="D16" s="27">
+        <v>236.1745297875832</v>
+      </c>
+      <c r="E16" s="27">
+        <v>231.05728375859695</v>
+      </c>
+      <c r="F16" s="27">
+        <v>225.97376346762789</v>
+      </c>
+      <c r="G16" s="27">
+        <v>221.84259467046297</v>
+      </c>
+      <c r="H16" s="27">
+        <v>216.2083165941149</v>
       </c>
     </row>
   </sheetData>
@@ -4633,32 +5497,32 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:T16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="10.83203125" style="6"/>
+    <col min="8" max="12" width="10.77734375" style="6"/>
     <col min="13" max="13" width="13" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="10.83203125" style="6"/>
+    <col min="14" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4672,30 +5536,30 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -4703,30 +5567,30 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:20" ht="31" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>27</v>
+    <row r="6" spans="1:20" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C6" s="19">
-        <v>49.637573506113846</v>
+        <v>48.714692711221161</v>
       </c>
       <c r="D6" s="19">
-        <v>44.956233089046592</v>
+        <v>44.038623887588642</v>
       </c>
       <c r="E6" s="19">
-        <v>43.530610755301957</v>
+        <v>42.610025924159046</v>
       </c>
       <c r="F6" s="19">
-        <v>41.978189136184469</v>
+        <v>41.040663377197866</v>
       </c>
       <c r="G6" s="19">
-        <v>40.72659205812144</v>
+        <v>39.760530988522142</v>
       </c>
       <c r="H6" s="19">
-        <v>39.032451987648663</v>
+        <v>38.057143333393292</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -4734,30 +5598,30 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:20" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>29</v>
+    <row r="7" spans="1:20" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" s="19">
-        <v>68.94836751279955</v>
+        <v>68.962924730502692</v>
       </c>
       <c r="D7" s="19">
-        <v>63.784605233713762</v>
+        <v>63.781014987540637</v>
       </c>
       <c r="E7" s="19">
-        <v>62.13877450366622</v>
+        <v>62.121518662324831</v>
       </c>
       <c r="F7" s="19">
-        <v>60.381153727366154</v>
+        <v>60.336995612726852</v>
       </c>
       <c r="G7" s="19">
-        <v>58.940191609378331</v>
+        <v>58.858305502218954</v>
       </c>
       <c r="H7" s="19">
-        <v>57.073407067248155</v>
+        <v>56.97389238963067</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -4765,30 +5629,30 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="E8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="F8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="G8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="H8" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -4803,30 +5667,30 @@
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:20" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>9.4310420240237058E-2</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.1230310492526331</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.15430618035722421</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.17952089150560194</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0.21365108665432553</v>
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>9.598888063098493E-2</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.12531469352070732</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.15753007782507525</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.18380823575710409</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.21877484563036076</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -4834,30 +5698,30 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:20" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>29</v>
+    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>7.4893176812738729E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>9.876365829646655E-2</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.12425549863588839</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.14515464636002157</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.17222975501699778</v>
+        <v>27</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>7.5140515910719019E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>9.920411721099566E-2</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.12508067416636903</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.14652248679665419</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.17384750411505104</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -4865,30 +5729,30 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="E11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="F11" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="G11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="H11" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
@@ -4896,56 +5760,134 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="1:20" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>5.0857631123313624E-2</v>
-      </c>
-      <c r="E12" s="21">
-        <v>6.6345454761690251E-2</v>
-      </c>
-      <c r="F12" s="21">
-        <v>8.3210813615981025E-2</v>
-      </c>
-      <c r="G12" s="21">
-        <v>9.6808043648447653E-2</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0.11521301810003989</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>5.0800361040292445E-2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>6.6320511632787946E-2</v>
+      </c>
+      <c r="F12" s="23">
+        <v>8.3369915094477928E-2</v>
+      </c>
+      <c r="G12" s="23">
+        <v>9.7277149991328846E-2</v>
+      </c>
+      <c r="H12" s="24">
+        <v>0.11578258931138175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>5.6295768037089321E-2</v>
+      </c>
+      <c r="E13" s="25">
+        <v>7.4324376179026846E-2</v>
+      </c>
+      <c r="F13" s="25">
+        <v>9.3711262605107676E-2</v>
+      </c>
+      <c r="G13" s="25">
+        <v>0.1097756094557935</v>
+      </c>
+      <c r="H13" s="26">
+        <v>0.130247691899221</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>5.6098615738513033E-2</v>
-      </c>
-      <c r="E13" s="23">
-        <v>7.3978762171574577E-2</v>
-      </c>
-      <c r="F13" s="23">
-        <v>9.30733848932737E-2</v>
-      </c>
-      <c r="G13" s="23">
-        <v>0.10872785846928508</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0.12900842582222247</v>
+      <c r="B14" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="27">
+        <v>184.08251558546596</v>
+      </c>
+      <c r="D15" s="27">
+        <v>166.41264097068128</v>
+      </c>
+      <c r="E15" s="27">
+        <v>161.01427156235246</v>
+      </c>
+      <c r="F15" s="27">
+        <v>155.08398257905188</v>
+      </c>
+      <c r="G15" s="27">
+        <v>150.24663316197183</v>
+      </c>
+      <c r="H15" s="27">
+        <v>143.80989165500714</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>260.59629980172048</v>
+      </c>
+      <c r="D16" s="27">
+        <v>241.0149593901948</v>
+      </c>
+      <c r="E16" s="27">
+        <v>234.74407393143883</v>
+      </c>
+      <c r="F16" s="27">
+        <v>228.00073893726005</v>
+      </c>
+      <c r="G16" s="27">
+        <v>222.41308190476593</v>
+      </c>
+      <c r="H16" s="27">
+        <v>215.29228349957381</v>
       </c>
     </row>
   </sheetData>
@@ -4961,30 +5903,30 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4998,30 +5940,30 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -5029,30 +5971,30 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>27</v>
+    <row r="6" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C6" s="19">
-        <v>8.8942997457191915</v>
+        <v>9.2436520955617016</v>
       </c>
       <c r="D6" s="19">
-        <v>8.0800651142341611</v>
+        <v>8.3979685717456523</v>
       </c>
       <c r="E6" s="19">
-        <v>7.8344344501704111</v>
+        <v>8.1433658986683</v>
       </c>
       <c r="F6" s="19">
-        <v>7.5703083537960625</v>
+        <v>7.8694339277805163</v>
       </c>
       <c r="G6" s="19">
-        <v>7.3545446042055964</v>
+        <v>7.645964452134435</v>
       </c>
       <c r="H6" s="19">
-        <v>7.064289174638323</v>
+        <v>7.3449694520921307</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -5060,30 +6002,30 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>29</v>
+    <row r="7" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" s="19">
-        <v>12.330084779855367</v>
+        <v>12.771951807629844</v>
       </c>
       <c r="D7" s="19">
-        <v>11.447190082485328</v>
+        <v>11.855759422436916</v>
       </c>
       <c r="E7" s="19">
-        <v>11.17086667950587</v>
+        <v>11.569637553367111</v>
       </c>
       <c r="F7" s="19">
-        <v>10.878647197892032</v>
+        <v>11.266855732425647</v>
       </c>
       <c r="G7" s="19">
-        <v>10.637532272082394</v>
+        <v>11.017352454645264</v>
       </c>
       <c r="H7" s="19">
-        <v>10.324821394070428</v>
+        <v>10.693297352910163</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -5091,30 +6033,30 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="E8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="F8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="G8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="H8" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -5122,30 +6064,30 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:13" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:13" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>9.1545670234120441E-2</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.11916230910239914</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.14885841828755134</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.1731170733541644</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0.20575094424512158</v>
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>9.1488030388129873E-2</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.11903154570493833</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.14866614986959645</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.17284160274642846</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.20540394898475409</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -5153,30 +6095,30 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>29</v>
+    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>7.1604917008558949E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>9.4015420092115096E-2</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.11771513398956208</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.13727014355474909</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.16263175976381739</v>
+        <v>27</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>7.1734719876221445E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>9.4137080406495252E-2</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.11784385800023661</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.13737910848805412</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.16275151096936588</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -5184,30 +6126,30 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="E11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="F11" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="G11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="H11" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
@@ -5215,30 +6157,30 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>9.475808681412444E-2</v>
-      </c>
-      <c r="E12" s="21">
-        <v>0.12334381737573563</v>
-      </c>
-      <c r="F12" s="21">
-        <v>0.15408198866239439</v>
-      </c>
-      <c r="G12" s="21">
-        <v>0.1791919008725216</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0.21297092245877347</v>
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>9.8418010814502146E-2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>0.12804787580141708</v>
+      </c>
+      <c r="F12" s="23">
+        <v>0.15992722417942332</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0.18593390475374075</v>
+      </c>
+      <c r="H12" s="24">
+        <v>0.22096276405515261</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
@@ -5246,30 +6188,108 @@
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
     </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>0.1066236121843796</v>
+      </c>
+      <c r="E13" s="25">
+        <v>0.13992158289251286</v>
+      </c>
+      <c r="F13" s="25">
+        <v>0.17515838683707388</v>
+      </c>
+      <c r="G13" s="25">
+        <v>0.20419480010434321</v>
+      </c>
+      <c r="H13" s="26">
+        <v>0.24190732211629748</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>0.10274853113105202</v>
-      </c>
-      <c r="E13" s="23">
-        <v>0.13490618691700973</v>
-      </c>
-      <c r="F13" s="23">
-        <v>0.16891377875456173</v>
-      </c>
-      <c r="G13" s="23">
-        <v>0.19697398178274864</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0.23336629842044221</v>
+      <c r="B14" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="27">
+        <v>196.77736068578804</v>
+      </c>
+      <c r="D15" s="27">
+        <v>178.77458753167062</v>
+      </c>
+      <c r="E15" s="27">
+        <v>173.35464728362044</v>
+      </c>
+      <c r="F15" s="27">
+        <v>167.52322809113099</v>
+      </c>
+      <c r="G15" s="27">
+        <v>162.76604628064433</v>
+      </c>
+      <c r="H15" s="27">
+        <v>156.35851373012983</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>271.887230450635</v>
+      </c>
+      <c r="D16" s="27">
+        <v>252.38347613633701</v>
+      </c>
+      <c r="E16" s="27">
+        <v>246.29256037620425</v>
+      </c>
+      <c r="F16" s="27">
+        <v>239.84699027333281</v>
+      </c>
+      <c r="G16" s="27">
+        <v>234.53560512204066</v>
+      </c>
+      <c r="H16" s="27">
+        <v>227.63717288151798</v>
       </c>
     </row>
   </sheetData>
@@ -5285,30 +6305,30 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5322,30 +6342,30 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -5353,30 +6373,30 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>27</v>
+    <row r="6" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C6" s="19">
-        <v>13.005055146912591</v>
+        <v>13.050139317519012</v>
       </c>
       <c r="D6" s="19">
-        <v>11.769080169181498</v>
+        <v>11.805602952317628</v>
       </c>
       <c r="E6" s="19">
-        <v>11.401641365400094</v>
+        <v>11.433656511241345</v>
       </c>
       <c r="F6" s="19">
-        <v>10.996598149782509</v>
+        <v>11.023943475516056</v>
       </c>
       <c r="G6" s="19">
-        <v>10.669492144391425</v>
+        <v>10.691996553957386</v>
       </c>
       <c r="H6" s="19">
-        <v>10.229591327039566</v>
+        <v>10.24707414580336</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -5384,30 +6404,30 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>29</v>
+    <row r="7" spans="1:13" s="9" customFormat="1" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" s="19">
-        <v>18.142681993876469</v>
+        <v>18.372026188711963</v>
       </c>
       <c r="D7" s="19">
-        <v>16.740150891668645</v>
+        <v>16.954960194837113</v>
       </c>
       <c r="E7" s="19">
-        <v>16.295761775415219</v>
+        <v>16.503303632750182</v>
       </c>
       <c r="F7" s="19">
-        <v>15.818290306718167</v>
+        <v>16.018564718219615</v>
       </c>
       <c r="G7" s="19">
-        <v>15.423526631092914</v>
+        <v>15.616533596760849</v>
       </c>
       <c r="H7" s="19">
-        <v>14.921005800790946</v>
+        <v>15.106745320625375</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -5415,30 +6435,30 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="E8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="F8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="G8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="H8" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -5446,30 +6466,30 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:13" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:13" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>9.5038042035870518E-2</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.12329157880527317</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.15443663824884982</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.17958885803537944</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0.2134142291993219</v>
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>9.5365753186302776E-2</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.12386709190971144</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.15526239166526845</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.18069866582925773</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.21479197298320857</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -5477,30 +6497,30 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>29</v>
+    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>7.7305610200366595E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>0.10179973496116085</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.12811731407422741</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.14987615192182316</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.17757441783816227</v>
+        <v>27</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>7.7131720764991918E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>0.10171564838667341</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.12810026756538964</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.14998305378228388</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.17773112418557424</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -5508,82 +6528,160 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="E11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="F11" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="G11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="H11" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="14" t="s">
+    </row>
+    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="B12" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>8.0426334462597532E-2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>0.10446282685334687</v>
+      </c>
+      <c r="F12" s="23">
+        <v>0.13093992994675166</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0.15239151214522537</v>
+      </c>
+      <c r="H12" s="24">
+        <v>0.18114396921168463</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+      <c r="B13" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>7.9873067373420842E-2</v>
-      </c>
-      <c r="E12" s="21">
-        <v>0.10361826032539863</v>
-      </c>
-      <c r="F12" s="21">
-        <v>0.1297935831539884</v>
-      </c>
-      <c r="G12" s="21">
-        <v>0.15093232825610561</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0.1793602723933472</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>9.1575808281431761E-2</v>
+      </c>
+      <c r="E13" s="25">
+        <v>0.12076345015379486</v>
+      </c>
+      <c r="F13" s="25">
+        <v>0.15208899045712171</v>
+      </c>
+      <c r="G13" s="25">
+        <v>0.17806966112525746</v>
+      </c>
+      <c r="H13" s="26">
+        <v>0.21101397962650767</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>9.0636512258208943E-2</v>
-      </c>
-      <c r="E13" s="23">
-        <v>0.1193545061189611</v>
-      </c>
-      <c r="F13" s="23">
-        <v>0.15021039841067643</v>
-      </c>
-      <c r="G13" s="23">
-        <v>0.17572142106720076</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0.20819609155684002</v>
+      <c r="B14" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="27">
+        <v>185.19136613351787</v>
+      </c>
+      <c r="D15" s="27">
+        <v>167.53045201859459</v>
+      </c>
+      <c r="E15" s="27">
+        <v>162.25225016377237</v>
+      </c>
+      <c r="F15" s="27">
+        <v>156.43811171186951</v>
+      </c>
+      <c r="G15" s="27">
+        <v>151.72753335009364</v>
+      </c>
+      <c r="H15" s="27">
+        <v>145.41374722224384</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>260.71297368916998</v>
+      </c>
+      <c r="D16" s="27">
+        <v>240.60373340276624</v>
+      </c>
+      <c r="E16" s="27">
+        <v>234.19438452755836</v>
+      </c>
+      <c r="F16" s="27">
+        <v>227.31557200181891</v>
+      </c>
+      <c r="G16" s="27">
+        <v>221.61044573460805</v>
+      </c>
+      <c r="H16" s="27">
+        <v>214.37616378562973</v>
       </c>
     </row>
   </sheetData>
@@ -5599,30 +6697,30 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5636,30 +6734,30 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -5667,30 +6765,30 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>27</v>
+    <row r="6" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C6" s="19">
-        <v>16.243691911656686</v>
+        <v>17.03293792049277</v>
       </c>
       <c r="D6" s="19">
-        <v>14.599494264010053</v>
+        <v>15.331828170706968</v>
       </c>
       <c r="E6" s="19">
-        <v>14.012430552939444</v>
+        <v>14.732187771598461</v>
       </c>
       <c r="F6" s="19">
-        <v>13.406582485883982</v>
+        <v>14.113314770847159</v>
       </c>
       <c r="G6" s="19">
-        <v>12.879883706811565</v>
+        <v>13.570582400856209</v>
       </c>
       <c r="H6" s="19">
-        <v>12.208166927728005</v>
+        <v>12.883818532018777</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -5698,30 +6796,30 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>29</v>
+    <row r="7" spans="1:13" s="9" customFormat="1" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" s="19">
-        <v>27.50984948465954</v>
+        <v>28.113035464234081</v>
       </c>
       <c r="D7" s="19">
-        <v>25.444283034872122</v>
+        <v>25.997515797015808</v>
       </c>
       <c r="E7" s="19">
-        <v>24.66109394654449</v>
+        <v>25.20498902145377</v>
       </c>
       <c r="F7" s="19">
-        <v>23.869524954495844</v>
+        <v>24.403462267503635</v>
       </c>
       <c r="G7" s="19">
-        <v>23.168081510840818</v>
+        <v>23.688871132332327</v>
       </c>
       <c r="H7" s="19">
-        <v>22.333210818242613</v>
+        <v>22.841647828707888</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -5729,30 +6827,30 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="E8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="F8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="G8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="H8" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -5760,30 +6858,30 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:13" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:13" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>0.10122068656490188</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.13736171375646813</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.17465915022290943</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.20708396977359611</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0.24843643956536357</v>
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>9.987177536408165E-2</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.13507652993475758</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.17141042627372796</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.20327412310185855</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.24359387721844977</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -5791,30 +6889,30 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>29</v>
+    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>7.5084614728235827E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>0.10355402124986603</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.13232804244144153</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.15782594434912647</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.18817400906913734</v>
+        <v>27</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>7.525048904483031E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>0.10344121133699635</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.13195206904817636</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.15737056702860339</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.18750688242941779</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -5822,82 +6920,160 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="E11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="F11" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="G11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="H11" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="14" t="s">
+    </row>
+    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="B12" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>5.5902944812292056E-2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>7.5608706973025422E-2</v>
+      </c>
+      <c r="F12" s="23">
+        <v>9.5946503056537319E-2</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0.11378211756128574</v>
+      </c>
+      <c r="H12" s="24">
+        <v>0.13635098630331094</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+      <c r="B13" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>5.4032663306094061E-2</v>
-      </c>
-      <c r="E12" s="21">
-        <v>7.3325122387827055E-2</v>
-      </c>
-      <c r="F12" s="21">
-        <v>9.3234884859942635E-2</v>
-      </c>
-      <c r="G12" s="21">
-        <v>0.11054359335620187</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0.13261797511512549</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>6.9521545697279627E-2</v>
+      </c>
+      <c r="E13" s="25">
+        <v>9.5566061991473494E-2</v>
+      </c>
+      <c r="F13" s="25">
+        <v>0.12190634126933433</v>
+      </c>
+      <c r="G13" s="25">
+        <v>0.14538968724267018</v>
+      </c>
+      <c r="H13" s="26">
+        <v>0.17323167544605825</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>6.7879951462936378E-2</v>
-      </c>
-      <c r="E13" s="23">
-        <v>9.3617606771702819E-2</v>
-      </c>
-      <c r="F13" s="23">
-        <v>0.11963064777813349</v>
-      </c>
-      <c r="G13" s="23">
-        <v>0.14268192599491439</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0.17011797487982275</v>
+      <c r="B14" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="27">
+        <v>116.69637561082186</v>
+      </c>
+      <c r="D15" s="27">
+        <v>105.04170140001536</v>
+      </c>
+      <c r="E15" s="27">
+        <v>100.93343413734895</v>
+      </c>
+      <c r="F15" s="27">
+        <v>96.693400122771806</v>
+      </c>
+      <c r="G15" s="27">
+        <v>92.975022189366939</v>
+      </c>
+      <c r="H15" s="27">
+        <v>88.269853018441211</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>192.60854242576278</v>
+      </c>
+      <c r="D16" s="27">
+        <v>178.11465541401219</v>
+      </c>
+      <c r="E16" s="27">
+        <v>172.68488148338864</v>
+      </c>
+      <c r="F16" s="27">
+        <v>167.19344673632997</v>
+      </c>
+      <c r="G16" s="27">
+        <v>162.2976268896677</v>
+      </c>
+      <c r="H16" s="27">
+        <v>156.4931151062338</v>
       </c>
     </row>
   </sheetData>
@@ -5913,30 +7089,30 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5950,30 +7126,30 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -5981,30 +7157,30 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>27</v>
+    <row r="6" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C6" s="19">
-        <v>4.3121590047465057</v>
+        <v>4.2134590219747965</v>
       </c>
       <c r="D6" s="19">
-        <v>3.9122423081946947</v>
+        <v>3.8189732338171578</v>
       </c>
       <c r="E6" s="19">
-        <v>3.7705531260117313</v>
+        <v>3.6803170271954779</v>
       </c>
       <c r="F6" s="19">
-        <v>3.6277313611925313</v>
+        <v>3.5392520460879124</v>
       </c>
       <c r="G6" s="19">
-        <v>3.506196364326911</v>
+        <v>3.4192676534677822</v>
       </c>
       <c r="H6" s="19">
-        <v>3.3455437113956101</v>
+        <v>3.2613303356273877</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -6012,30 +7188,30 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>29</v>
+    <row r="7" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" s="19">
-        <v>7.2995857545014591</v>
+        <v>7.1258747981201669</v>
       </c>
       <c r="D7" s="19">
-        <v>6.8451417882576555</v>
+        <v>6.6782308595596431</v>
       </c>
       <c r="E7" s="19">
-        <v>6.6794641318042007</v>
+        <v>6.5161885026610484</v>
       </c>
       <c r="F7" s="19">
-        <v>6.5149944515528713</v>
+        <v>6.3540191612774128</v>
       </c>
       <c r="G7" s="19">
-        <v>6.3742807305844327</v>
+        <v>6.2153376010537675</v>
       </c>
       <c r="H7" s="19">
-        <v>6.197056779118463</v>
+        <v>6.041245071612777</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -6043,30 +7219,30 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="E8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="F8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="G8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="H8" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -6074,30 +7250,30 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>9.2741639654663088E-2</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.1255997003214897</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.15872040961397924</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.18690466644027984</v>
-      </c>
-      <c r="H9" s="22">
-        <v>0.22416040138754553</v>
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>9.3625163102392786E-2</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.12653309122001177</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.16001270508877324</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.18848916397786317</v>
+      </c>
+      <c r="H9" s="24">
+        <v>0.22597316869149417</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -6105,30 +7281,30 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>29</v>
+    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>6.2256130899422633E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>8.4952988231537102E-2</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.10748435998094157</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0.12676130605718489</v>
-      </c>
-      <c r="H10" s="22">
-        <v>0.1510399373968716</v>
+        <v>27</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>6.2819506550776602E-2</v>
+      </c>
+      <c r="E10" s="23">
+        <v>8.5559501497269652E-2</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.10831731663968788</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.12777900578699511</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.15221004539590274</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -6136,30 +7312,30 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="E11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="F11" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="G11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="H11" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>26</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
@@ -6167,56 +7343,134 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="1:13" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:13" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
-        <v>9.0366639974446314E-2</v>
-      </c>
-      <c r="E12" s="21">
-        <v>0.12238324599515235</v>
-      </c>
-      <c r="F12" s="21">
-        <v>0.15465577453225388</v>
-      </c>
-      <c r="G12" s="21">
-        <v>0.18211826709819781</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0.21841992835304794</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>8.9139452043004719E-2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>0.1204707158087837</v>
+      </c>
+      <c r="F12" s="23">
+        <v>0.15234627507065596</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0.1794583874279134</v>
+      </c>
+      <c r="H12" s="24">
+        <v>0.2151464816307109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>0.10115126220393067</v>
+      </c>
+      <c r="E13" s="25">
+        <v>0.1377669460519016</v>
+      </c>
+      <c r="F13" s="25">
+        <v>0.17441132377872526</v>
+      </c>
+      <c r="G13" s="25">
+        <v>0.20574831653716849</v>
+      </c>
+      <c r="H13" s="26">
+        <v>0.24508690146218304</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>0.10268782133929451</v>
-      </c>
-      <c r="E13" s="23">
-        <v>0.14012495077557371</v>
-      </c>
-      <c r="F13" s="23">
-        <v>0.17728912148945808</v>
-      </c>
-      <c r="G13" s="23">
-        <v>0.20908530872509704</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0.2491314812281728</v>
+      <c r="B14" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="27">
+        <v>108.6631795474281</v>
+      </c>
+      <c r="D15" s="27">
+        <v>98.48957163907555</v>
+      </c>
+      <c r="E15" s="27">
+        <v>94.913691537496859</v>
+      </c>
+      <c r="F15" s="27">
+        <v>91.275690244497071</v>
+      </c>
+      <c r="G15" s="27">
+        <v>88.181347679356961</v>
+      </c>
+      <c r="H15" s="27">
+        <v>84.108216545003017</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="27">
+        <v>183.77304931227511</v>
+      </c>
+      <c r="D16" s="27">
+        <v>172.22851703714639</v>
+      </c>
+      <c r="E16" s="27">
+        <v>168.0495188244837</v>
+      </c>
+      <c r="F16" s="27">
+        <v>163.86724574007641</v>
+      </c>
+      <c r="G16" s="27">
+        <v>160.29071178070819</v>
+      </c>
+      <c r="H16" s="27">
+        <v>155.8009451339102</v>
       </c>
     </row>
   </sheetData>
